--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Library/Application Support/Box/Box Edit/Documents/2210800833080/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Library/CloudStorage/Box-Box/Prod/Team Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225EAAC3-B5A1-A246-A76F-CF316194CA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167DBD36-C070-C94D-8641-1827672FF0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t/>
   </si>
@@ -113,27 +113,6 @@
   </si>
   <si>
     <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report; Update：2026/4/23- 每月第一周/二周发出；</t>
-  </si>
-  <si>
-    <t>Item 7</t>
-  </si>
-  <si>
-    <t>氮气发生装置的讨论；</t>
-  </si>
-  <si>
-    <t>Udpate 4/9四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)</t>
-  </si>
-  <si>
-    <t>Item 8</t>
-  </si>
-  <si>
-    <t>4/16/2026</t>
-  </si>
-  <si>
-    <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
-  </si>
-  <si>
-    <t>Update : 4/23 需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进-行；</t>
   </si>
 </sst>
 </file>
@@ -520,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -766,69 +745,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="80">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="80">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Library/CloudStorage/Box-Box/Prod/Team Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/Data Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167DBD36-C070-C94D-8641-1827672FF0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C03BD2A5-A705-B94B-89F7-3CF07692EF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
   <si>
     <t/>
   </si>
@@ -58,11 +58,6 @@
     <t>BM 26项目Engineering Engagement</t>
   </si>
   <si>
-    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;
-Update: 2026/4/27 - 做一个测试-4/27
-Update: 2026/4/27 - 接着做一个测试测试；接着做一个测试测试；接着做一个测试测试；接着做一个测试测试；接着做一个测试测试；接着做一个测试测试</t>
-  </si>
-  <si>
     <t>Done</t>
   </si>
   <si>
@@ -72,10 +67,6 @@
     <t>GYA冷机修复同步；</t>
   </si>
   <si>
-    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项；（是否需要加入大保）/ 维保中增加震动测试;JCI检测报告的安排和计划；
-Update: 2026/4/27 - 接着做一个测试测试</t>
-  </si>
-  <si>
     <t>Ongoing</t>
   </si>
   <si>
@@ -113,6 +104,76 @@
   </si>
   <si>
     <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report; Update：2026/4/23- 每月第一周/二周发出；</t>
+  </si>
+  <si>
+    <t>Item 7</t>
+  </si>
+  <si>
+    <t>氮气发生装置的讨论；</t>
+  </si>
+  <si>
+    <t>Udpate 4/9四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)</t>
+  </si>
+  <si>
+    <t>Item 8</t>
+  </si>
+  <si>
+    <t>4/16/2026</t>
+  </si>
+  <si>
+    <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
+  </si>
+  <si>
+    <t>Update : 4/23 需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进-行；</t>
+  </si>
+  <si>
+    <t>Item 9</t>
+  </si>
+  <si>
+    <t>电池回收关注（EHS，Compliance)</t>
+  </si>
+  <si>
+    <t>Udpate: 4/23需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）</t>
+  </si>
+  <si>
+    <t>Item 10</t>
+  </si>
+  <si>
+    <t>4/23/2026</t>
+  </si>
+  <si>
+    <t>ULA domestic water 环网修复计划？</t>
+  </si>
+  <si>
+    <t>Udpate: 4/235月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；</t>
+  </si>
+  <si>
+    <t>Item 11</t>
+  </si>
+  <si>
+    <t>岩棉问题（ULA+GYA）的讨论</t>
+  </si>
+  <si>
+    <t>Udpate: 4/23DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境；_x000D_
+Update: 2026/4/24 - 做一个测试-测试I</t>
+  </si>
+  <si>
+    <t>Item 12</t>
+  </si>
+  <si>
+    <t>变电站OPS预算（FY27+FY26）</t>
+  </si>
+  <si>
+    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项；（是否需要加入大保）/ 维保中增加震动测试;JCI检测报告的安排和计划；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -499,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -571,7 +632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="112">
+    <row r="3" spans="1:9" ht="48">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -591,21 +652,21 @@
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="80">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="96">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -614,16 +675,16 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" t="s">
         <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -634,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
@@ -643,16 +704,16 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -663,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -672,27 +733,27 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="224" customHeight="1">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="208">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
@@ -701,16 +762,16 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
@@ -721,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
@@ -730,18 +791,192 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="80">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="80">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="48">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="48">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="48">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
         <v>0</v>
       </c>
     </row>
@@ -749,7 +984,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I8" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I2 A5:I13 A3:F3 H3:I3 A4:F4 H4:I4 A14:F14 H14:I14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/Data Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C03BD2A5-A705-B94B-89F7-3CF07692EF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{643A39BD-7EF6-A646-B148-87039999B9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
   <si>
     <t/>
   </si>
@@ -58,6 +58,9 @@
     <t>BM 26项目Engineering Engagement</t>
   </si>
   <si>
+    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;</t>
+  </si>
+  <si>
     <t>Done</t>
   </si>
   <si>
@@ -94,85 +97,125 @@
     <t>ULA水管修复方案同步；</t>
   </si>
   <si>
-    <t>Update: 4/17- 6个Options from Places Team. (已经讨论并做了进一步评估）Principles for decision:  - Ops stability(稳定性可靠性） as the first priority. - 质量可靠性，施工难易；（Piority 2)- 交付后的可维护性；(Piority 3)方案2；- 最大化利用原有管道，便于以后维修；- 施工成本低；- 不太美观；是否存在对结构的影响；需要结构专家的评估和报告；（Decision Point)方案6:施工的难易来讲，方案2更简单，更便于施工和维护；防冻考虑；（冻土层以下）结构影响；Actions：Place team提供结构工程的专业建议；（Communicate with Places team in regular meeting)-Update 4/23 Option 6/7 may prefer. (TBD) Waiting for US team further feedback.</t>
-  </si>
-  <si>
     <t>Item 6</t>
   </si>
   <si>
+    <t>Item 7</t>
+  </si>
+  <si>
+    <t>氮气发生装置的讨论；</t>
+  </si>
+  <si>
+    <t>Item 8</t>
+  </si>
+  <si>
+    <t>4/16/2026</t>
+  </si>
+  <si>
+    <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
+  </si>
+  <si>
+    <t>Item 9</t>
+  </si>
+  <si>
+    <t>电池回收关注（EHS，Compliance)</t>
+  </si>
+  <si>
+    <t>Item 10</t>
+  </si>
+  <si>
+    <t>4/23/2026</t>
+  </si>
+  <si>
+    <t>ULA domestic water 环网修复计划？</t>
+  </si>
+  <si>
+    <t>Item 11</t>
+  </si>
+  <si>
+    <t>岩棉问题（ULA+GYA）的讨论</t>
+  </si>
+  <si>
+    <t>Item 12</t>
+  </si>
+  <si>
+    <t>变电站OPS预算（FY27+FY26）</t>
+  </si>
+  <si>
+    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；</t>
+  </si>
+  <si>
+    <t>Item 13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/26/2026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GYA烟雾报警/应急疏散讨论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GYA- incident-[P1]-captured the smoke alarm message in the corridor of 0130 area.
+Leadershop high atttion.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update : 4/25 
+屋顶施工导致（亚弧焊）：烟通过伸缩缝和女儿墙拼接（DH）进入室内，引起报警(3个烟感，7个ASD);
+Team Concerns：
+没有启动人员疏散（US point, 发现烟雾，第一时间启动人员疏散），需要明确Trigger人员疏散的前提；
+需要明确广播通知的条件；
+RCA syncing；（TBD）
+初步判断：立墙伸缩缝的塑料薄膜融化后禅师的烟雾；封堵请款重点关注；（岩绵和挡水条之间有塑料，需要确认）；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate 4/9 
+四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)
+Update 4/25
+厂家沟通（一共4四家）：Mesa/Reno DC使用的厂家（AODC在使用），德国一家已经沟通，另外两家这周沟通，并确定下一步Engineering Team行动计划；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update : 4/23 
+需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进-行；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+5月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境；Update: 2026/4/24 - 做一个测试-测试I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项；（是否需要加入大保）/ 维保中增加震动测试;JCI检测报告的安排和计划；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update: 4/17 
+6个Options from Places Team. (已经讨论并做了进一步评估）Principles for decision:  - Ops stability(稳定性可靠性） as the first priority. - 质量可靠性，施工难易；（Piority 2)- 交付后的可维护性；(Piority 3)方案2；- 最大化利用原有管道，便于以后维修；- 施工成本低；- 不太美观；是否存在对结构的影响；需要结构专家的评估和报告；（Decision Point)方案6:施工的难易来讲，方案2更简单，更便于施工和维护；防冻考虑；（冻土层以下）结构影响；Actions：Place team提供结构工程的专业建议；（Communicate with Places team in regular meeting)
+Update 4/23 
+Option 6/7 may prefer. (TBD) Waiting for US team further feedback.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
-  </si>
-  <si>
-    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report; Update：2026/4/23- 每月第一周/二周发出；</t>
-  </si>
-  <si>
-    <t>Item 7</t>
-  </si>
-  <si>
-    <t>氮气发生装置的讨论；</t>
-  </si>
-  <si>
-    <t>Udpate 4/9四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)</t>
-  </si>
-  <si>
-    <t>Item 8</t>
-  </si>
-  <si>
-    <t>4/16/2026</t>
-  </si>
-  <si>
-    <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
-  </si>
-  <si>
-    <t>Update : 4/23 需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进-行；</t>
-  </si>
-  <si>
-    <t>Item 9</t>
-  </si>
-  <si>
-    <t>电池回收关注（EHS，Compliance)</t>
-  </si>
-  <si>
-    <t>Udpate: 4/23需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）</t>
-  </si>
-  <si>
-    <t>Item 10</t>
-  </si>
-  <si>
-    <t>4/23/2026</t>
-  </si>
-  <si>
-    <t>ULA domestic water 环网修复计划？</t>
-  </si>
-  <si>
-    <t>Udpate: 4/235月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；</t>
-  </si>
-  <si>
-    <t>Item 11</t>
-  </si>
-  <si>
-    <t>岩棉问题（ULA+GYA）的讨论</t>
-  </si>
-  <si>
-    <t>Udpate: 4/23DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境；_x000D_
-Update: 2026/4/24 - 做一个测试-测试I</t>
-  </si>
-  <si>
-    <t>Item 12</t>
-  </si>
-  <si>
-    <t>变电站OPS预算（FY27+FY26）</t>
-  </si>
-  <si>
-    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项；（是否需要加入大保）/ 维保中增加震动测试;JCI检测报告的安排和计划；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report; 
+Update：2026/4/23- 每月第一周/二周发出；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -569,7 +612,7 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="7" max="7" width="57.6640625" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
   </cols>
@@ -645,17 +688,17 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>0</v>
@@ -666,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -674,17 +717,17 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -695,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
@@ -703,17 +746,17 @@
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -724,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -732,28 +775,28 @@
       <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="224" customHeight="1">
+    <row r="7" spans="1:9" ht="224">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
@@ -761,17 +804,17 @@
       <c r="D7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
@@ -790,28 +833,28 @@
       <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="144">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="80">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
@@ -819,17 +862,17 @@
       <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
@@ -840,54 +883,54 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="64">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="48">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
@@ -898,54 +941,54 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="48">
+    <row r="13" spans="1:9" ht="64">
       <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
@@ -956,35 +999,55 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="160">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
+      <c r="H15" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I2 A5:I13 A3:F3 H3:I3 A4:F4 H4:I4 A14:F14 H14:I14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I3 A14:I14 A9:F9 H9:I9 A10:F10 H10:I10 A11:F11 H11:I11 A12:F12 H12:I12 A13:F13 H13:I13 A8:D8 H8:I8 A7:F7 H7:I7 A5:I6 A4:F4 H4:I4 F8" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/Data Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{643A39BD-7EF6-A646-B148-87039999B9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993AE8C6-B1BD-5D40-8517-0B601C63AEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,28 +194,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Udpate: 4/23
-DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境；Update: 2026/4/24 - 做一个测试-测试I</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项；（是否需要加入大保）/ 维保中增加震动测试;JCI检测报告的安排和计划；</t>
+DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report;
+Update：2026/4/23- 每月第一周/二周发出；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Update: 4/17 
 6个Options from Places Team. (已经讨论并做了进一步评估）Principles for decision:  - Ops stability(稳定性可靠性） as the first priority. - 质量可靠性，施工难易；（Piority 2)- 交付后的可维护性；(Piority 3)方案2；- 最大化利用原有管道，便于以后维修；- 施工成本低；- 不太美观；是否存在对结构的影响；需要结构专家的评估和报告；（Decision Point)方案6:施工的难易来讲，方案2更简单，更便于施工和维护；防冻考虑；（冻土层以下）结构影响；Actions：Place team提供结构工程的专业建议；（Communicate with Places team in regular meeting)
-Update 4/23 
-Option 6/7 may prefer. (TBD) Waiting for US team further feedback.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report; 
-Update：2026/4/23- 每月第一周/二周发出；</t>
+Update 4/23: Option 6/7 may prefer. (TBD) Waiting for US team further feedback.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项； 维保中增加震动测试;
+JCI检测报告的安排和计划；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -834,13 +834,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="64">
+    <row r="13" spans="1:9" ht="48">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>

--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/Data Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2895FEA1-3FB4-FC40-BC94-5B71B10E5FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E8D4B38-BF3F-344E-828E-5F5671A6ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$17</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -52,24 +55,24 @@
     <t>Item 1</t>
   </si>
   <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>BM 26项目Engineering Engagement</t>
+  </si>
+  <si>
+    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Item 2</t>
+  </si>
+  <si>
     <t>4/9/2026</t>
   </si>
   <si>
-    <t>BM 26项目Engineering Engagement</t>
-  </si>
-  <si>
-    <t>Weekly touch base wth Places team, including DCOE combination inputs;  DCOE internal syncing and call out;</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>Item 2</t>
-  </si>
-  <si>
-    <t>GYA冷机修复同步；</t>
-  </si>
-  <si>
     <t>Ongoing</t>
   </si>
   <si>
@@ -100,12 +103,12 @@
     <t>Item 6</t>
   </si>
   <si>
+    <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
+  </si>
+  <si>
     <t>Item 7</t>
   </si>
   <si>
-    <t>氮气发生装置的讨论；</t>
-  </si>
-  <si>
     <t>Item 8</t>
   </si>
   <si>
@@ -115,94 +118,76 @@
     <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
   </si>
   <si>
+    <t>Update : 4/23 _x000D_
+需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进行；</t>
+  </si>
+  <si>
     <t>Item 9</t>
   </si>
   <si>
-    <t>电池回收关注（EHS，Compliance)</t>
-  </si>
-  <si>
     <t>Item 10</t>
   </si>
   <si>
     <t>4/23/2026</t>
   </si>
   <si>
-    <t>ULA domestic water 环网修复计划？</t>
-  </si>
-  <si>
     <t>Item 11</t>
   </si>
   <si>
-    <t>岩棉问题（ULA+GYA）的讨论</t>
-  </si>
-  <si>
     <t>Item 12</t>
   </si>
   <si>
     <t>变电站OPS预算（FY27+FY26）</t>
   </si>
   <si>
+    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；_x000D_
+Update 4/30_x000D_
+Emily provided detail information of substation for team reference;
+Update: 2026/5/14 - Done</t>
+  </si>
+  <si>
     <t>Item 13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4/26/2026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GYA烟雾报警/应急疏散讨论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GYA- incident-[P1]-captured the smoke alarm message in the corridor of 0130 area.
-Leadershop high atttion.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate: 4/23
-需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate: 4/23
-5月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate: 4/23
-DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item 14</t>
+  </si>
+  <si>
+    <t>4/30/2026</t>
+  </si>
+  <si>
+    <t>Item 15</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
   </si>
   <si>
     <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项； 维保中增加震动测试;
-JCI检测报告的安排和计划；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4/30/2026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ULA冷机维修</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6000区域1#冷机2系统电流占比高限报警；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item 14</t>
+JCI检测报告的安排和计划；
+Update: 2026/5/14 - 
+检查报告已经出，检修的已经运送到ULA，报告预计在月底发出；
+Engineering重点关注：维修内容，更换清单。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Update: 4/17 
 6个Options from Places Team. (已经讨论并做了进一步评估）Principles for decision:  - Ops stability(稳定性可靠性） as the first priority. - 质量可靠性，施工难易；（Piority 2)- 交付后的可维护性；(Piority 3)方案2；- 最大化利用原有管道，便于以后维修；- 施工成本低；- 不太美观；是否存在对结构的影响；需要结构专家的评估和报告；（Decision Point)方案6:施工的难易来讲，方案2更简单，更便于施工和维护；防冻考虑；（冻土层以下）结构影响；Actions：Place team提供结构工程的专业建议；（Communicate with Places team in regular meeting)
 Update 4/23: Option 6/7 may prefer. (TBD) Waiting for US team further feedback.
-Update 4/30: EOP is under development，no feedback from US team.</t>
+Update 4/30: EOP is under development，no feedback from US team.
+Update: 2026/5/14 - EOP ready，pending final solution. (2/6/7 options)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report;
+Update 4/23
+每月第一周/二周发出;
+Update: 2026/5/14 - 已经发出；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Done</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -211,39 +196,90 @@
 Update 4/25
 厂家沟通（一共4四家）：Mesa/Reno DC使用的厂家（AODC在使用），德国一家已经沟通，另外两家这周沟通，并确定下一步Engineering Team行动计划；
 Update 4/30 
-3 qualified vendors have been identified from 4. (排除了一家没有自控系统的，下周五之前汇总技术要求给到qualified venders for comments. )</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Update : 4/23 
-需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进行；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">4月底前，初稿就绪，重点关注可能的增项和价格变化；
-Update 4/30
-Emily provided detail information of substation for team reference; </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Update 4/30
-Team alignment:  GYA买的新的的冷机做GYA三期的恢复，GYA修好的那台发到ULA做替换，ULA有故障的那台发回工厂维修，维修好后，做两个Site的备件；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Update 4/25 
+3 qualified vendors have been identified from 4. (排除了一家没有自控系统的，下周五之前汇总技术要求给到qualified venders for comments. )
+Update: 2026/5/14 - 月底有LDI的IFC图纸（计划），team review.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+5月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；
+Update: 2026/5/14 - 
+Prepare EOP;
+Solution: 是否可以从Small Enhancement, 从Ops Team来推进？（TBD） 
+Impact: 冷冻水补水/泄漏时候需要补充；消防需要两路供水；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Update 4/25 
 屋顶施工导致（亚弧焊）：烟通过伸缩缝和女儿墙拼接（DH）进入室内，引起报警(3个烟感，7个ASD);
 Team Concerns：
 没有启动人员疏散（US point, 发现烟雾，第一时间启动人员疏散），需要明确Trigger人员疏散的前提；
 需要明确广播通知的条件；
 RCA syncing；（TBD）
-初步判断：立墙伸缩缝的塑料薄膜融化后禅师的烟雾；封堵请款重点关注；（岩绵和挡水条之间有塑料，需要确认）；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report;
-Update 4/23
-每月第一周/二周发出;</t>
+初步判断：立墙伸缩缝的塑料薄膜融化后禅师的烟雾；封堵请款重点关注；（岩绵和挡水条之间有塑料，需要确认）；
+Update: 2026/5/14 - 
+Level 1 RCA has been send out for comments;
+重点关注：
+ASD灵敏度是否可以调整？是否影响预警一触发（提前报警这个功能）？可以调整，并触发早起报警的时间（基于灵敏度）；Engineering 澄清：ASD是监控，提前报警；联动（目前烟感+ASD）是启动灭火的要素；待定项（ASD是否拿出联动？案例：如果是自动模式，2022年的UPS事件会导致自喷，是否需要调整？）
+核心需求：改为自动模式（从运维和人生安全的角度），并加一道保护措施（和US一致），比如温控（联动条件）来做为一道保护措施；
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷机故障点：垫片有裂缝，需要追RCA（单独一项）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update: 2026/5/14
+垫片有裂缝，需要追RCA（单独一项）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update 4/30
+Team alignment:  GYA买的新的的冷机做GYA三期的恢复，GYA修好的那台发到ULA做替换，ULA有故障的那台发回工厂维修，维修好后，做两个Site的备件；
+Update: 2026/5/14 - 
+ULA坏的一台，计划发到无锡工厂，需要设备的RCA；（两台已经坏，需要原厂建议，维修内容，必要的时候工厂Visit）；
+重点关注：为什么会坏，需要采取什么措施，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GYA冷机修复同步；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>氮气发生装置的讨论；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池回收关注（EHS，Compliance)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）
+Update: 2026/5/14 - 通过BM26 Battery Refresh项目来做；（Apple Prefer)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ULA domestic water 环网修复计划？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩棉问题（ULA+GYA）的讨论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Udpate: 4/23
+DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境;
+Update: 2026/5/14 - 可选方案：用Patch方式，有问题的地方用铝箔胶带修复；（需要和DCO讨论），另外追溯一下破损原因（避免以后出现）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GYA烟雾报警/应急疏散讨论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ULA冷机维修</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -640,7 +676,7 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="57.6640625" customWidth="1"/>
+    <col min="7" max="7" width="85" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
   </cols>
@@ -703,7 +739,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="48">
+    <row r="3" spans="1:9" ht="32">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -716,10 +752,10 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -732,7 +768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="80">
+    <row r="4" spans="1:9" ht="112">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -743,16 +779,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -772,12 +808,12 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -790,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="32">
+    <row r="6" spans="1:9" ht="16">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -801,12 +837,12 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -819,7 +855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="256">
+    <row r="7" spans="1:9" ht="192">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -830,16 +866,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -859,45 +895,45 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="208">
+    <row r="9" spans="1:9" ht="176">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -906,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="80">
+    <row r="10" spans="1:9" ht="64">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -922,11 +958,11 @@
       <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -940,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
@@ -949,13 +985,13 @@
         <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -964,7 +1000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="48">
+    <row r="12" spans="1:9" ht="112">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -978,13 +1014,13 @@
         <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -993,12 +1029,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="48">
+    <row r="13" spans="1:9" ht="80">
       <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>0</v>
@@ -1007,13 +1043,10 @@
         <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1027,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>0</v>
@@ -1036,66 +1069,111 @@
         <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="335">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="160">
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="64">
+      <c r="I15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="112">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
       </c>
+      <c r="I16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:I17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I3 A14:F14 A9:F9 H9:I9 A10:F10 H10:I10 A11:F11 H11:I11 A12:F12 H12:I12 A13:F13 H13:I13 A8:D8 H8:I8 A7:F7 H7:I7 A5:I6 A4:F4 H4:I4 F8 H14:I14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I3 A5:I6 A4:D4 H4:I4 A10:I10 A7:F7 H7:I7 A8:F8 I8 A9:D9 H9:I9 A13:D13 A12:D12 H12:I12 A15:D15 A14:G14 I14 A17:D17 A16:D16 H16:I16 H15:I15 H17:I17 F4 F9 A11:D11 F11 H11:I11 F12 H13:I13 F15 F16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/team-inputs.xlsx
+++ b/team-inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelshi/Desktop/Prod/Data Source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E8D4B38-BF3F-344E-828E-5F5671A6ACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{452EBFFF-1F11-CB40-A746-D4BAAEABE4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$19</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="72">
   <si>
     <t/>
   </si>
@@ -73,6 +73,9 @@
     <t>4/9/2026</t>
   </si>
   <si>
+    <t>GYA冷机修复同步；</t>
+  </si>
+  <si>
     <t>Ongoing</t>
   </si>
   <si>
@@ -106,9 +109,18 @@
     <t>水顾问利田报告没有第一时间和Apple来分享的关注；（后续改进措施）</t>
   </si>
   <si>
+    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report;_x000D_
+Update 4/23_x000D_
+每月第一周/二周发出;_x000D_
+Update: 2026/5/14 - 已经发出；</t>
+  </si>
+  <si>
     <t>Item 7</t>
   </si>
   <si>
+    <t>氮气发生装置的讨论；</t>
+  </si>
+  <si>
     <t>Item 8</t>
   </si>
   <si>
@@ -118,31 +130,45 @@
     <t>PSG maintenance和spare parts这部分，看下FY27 or Future有没有需要做？</t>
   </si>
   <si>
-    <t>Update : 4/23 _x000D_
+    <t>Update : 4/23 _x000D__x000D_
 需要Double Confirm with DCO / PSG maintenance frequency; Team comments: - 元器件多，重要性高，关注度高； - 现场有过发电机停机报警； - 已经有预算计划；（50W+/Site) - 建议进行；</t>
   </si>
   <si>
     <t>Item 9</t>
   </si>
   <si>
+    <t>电池回收关注（EHS，Compliance)</t>
+  </si>
+  <si>
+    <t>Udpate: 4/23_x000D_
+需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）_x000D_
+Update: 2026/5/14 - 通过BM26 Battery Refresh项目来做；（Apple Prefer)</t>
+  </si>
+  <si>
     <t>Item 10</t>
   </si>
   <si>
     <t>4/23/2026</t>
   </si>
   <si>
+    <t>ULA domestic water 环网修复计划？</t>
+  </si>
+  <si>
     <t>Item 11</t>
   </si>
   <si>
+    <t>岩棉问题（ULA+GYA）的讨论</t>
+  </si>
+  <si>
     <t>Item 12</t>
   </si>
   <si>
     <t>变电站OPS预算（FY27+FY26）</t>
   </si>
   <si>
-    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；_x000D_
-Update 4/30_x000D_
-Emily provided detail information of substation for team reference;
+    <t>4月底前，初稿就绪，重点关注可能的增项和价格变化；_x000D__x000D_
+Update 4/30_x000D__x000D_
+Emily provided detail information of substation for team reference;_x000D_
 Update: 2026/5/14 - Done</t>
   </si>
   <si>
@@ -152,23 +178,51 @@
     <t>4/26/2026</t>
   </si>
   <si>
+    <t>GYA烟雾报警/应急疏散讨论</t>
+  </si>
+  <si>
     <t>Item 14</t>
   </si>
   <si>
     <t>4/30/2026</t>
   </si>
   <si>
+    <t>ULA冷机维修</t>
+  </si>
+  <si>
     <t>Item 15</t>
   </si>
   <si>
     <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>冷机故障点：垫片有裂缝，需要追RCA（单独一项）</t>
+  </si>
+  <si>
+    <t>Item 16</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>察哈尔园区警务站用电配套设施；</t>
+  </si>
+  <si>
+    <t>Item 17</t>
+  </si>
+  <si>
+    <t>ULA CBRE team stability</t>
+  </si>
+  <si>
+    <t>团队整体情况和稳定性的关注！</t>
   </si>
   <si>
     <t>现场沟通，CN，US沟通非常好！Team make decision. (Debate, different ideas, make decision base on principles, for example, Ops Priority in this case.)冷机维保的事项； 维保中增加震动测试;
 JCI检测报告的安排和计划；
 Update: 2026/5/14 - 
 检查报告已经出，检修的已经运送到ULA，报告预计在月底发出；
-Engineering重点关注：维修内容，更换清单。</t>
+Engineering重点关注：维修内容，更换清单。
+Update: 2026/5/21 - RCA需要重新修改；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -176,41 +230,21 @@
 6个Options from Places Team. (已经讨论并做了进一步评估）Principles for decision:  - Ops stability(稳定性可靠性） as the first priority. - 质量可靠性，施工难易；（Piority 2)- 交付后的可维护性；(Piority 3)方案2；- 最大化利用原有管道，便于以后维修；- 施工成本低；- 不太美观；是否存在对结构的影响；需要结构专家的评估和报告；（Decision Point)方案6:施工的难易来讲，方案2更简单，更便于施工和维护；防冻考虑；（冻土层以下）结构影响；Actions：Place team提供结构工程的专业建议；（Communicate with Places team in regular meeting)
 Update 4/23: Option 6/7 may prefer. (TBD) Waiting for US team further feedback.
 Update 4/30: EOP is under development，no feedback from US team.
-Update: 2026/5/14 - EOP ready，pending final solution. (2/6/7 options)</t>
+Update: 2026/5/14 - EOP ready，pending final solution. (2/6/7 options)
+Update: 2026/5/21 - 6/7 options pref..(US OPS team), Final decision will be decided next week.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>约定报告发出时间（整合和AIPO review后）：月初第一周内（before）发出；（厂家的原始报告）希望看到Consultant Report;
-Update 4/23
-每月第一周/二周发出;
-Update: 2026/5/14 - 已经发出；</t>
+    <t>Udpate: 4/23
+DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境;
+Update: 2026/5/14 - 可选方案：用Patch方式，有问题的地方用铝箔胶带修复；（需要和DCO讨论），另外追溯一下破损原因（避免以后出现）
+Update: 2026/5/21 - 
+1.小改会议上澄清
+2. 在GYA 2k/8K做测试，测试目的如下： Scope范围；只解决要解决的问题； Solution是否可行和影响，包含EHS； 灰尘是否可控；（需要观察和评估） 必要性做进一步评估；（每月起排烟风机影响）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Done</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate 4/9 
-四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)
-Update 4/25
-厂家沟通（一共4四家）：Mesa/Reno DC使用的厂家（AODC在使用），德国一家已经沟通，另外两家这周沟通，并确定下一步Engineering Team行动计划；
-Update 4/30 
-3 qualified vendors have been identified from 4. (排除了一家没有自控系统的，下周五之前汇总技术要求给到qualified venders for comments. )
-Update: 2026/5/14 - 月底有LDI的IFC图纸（计划），team review.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate: 4/23
-5月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；
-Update: 2026/5/14 - 
-Prepare EOP;
-Solution: 是否可以从Small Enhancement, 从Ops Team来推进？（TBD） 
-Impact: 冷冻水补水/泄漏时候需要补充；消防需要两路供水；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Update 4/25 
+    <t>Update 4/25 
 屋顶施工导致（亚弧焊）：烟通过伸缩缝和女儿墙拼接（DH）进入室内，引起报警(3个烟感，7个ASD);
 Team Concerns：
 没有启动人员疏散（US point, 发现烟雾，第一时间启动人员疏散），需要明确Trigger人员疏散的前提；
@@ -222,16 +256,9 @@
 重点关注：
 ASD灵敏度是否可以调整？是否影响预警一触发（提前报警这个功能）？可以调整，并触发早起报警的时间（基于灵敏度）；Engineering 澄清：ASD是监控，提前报警；联动（目前烟感+ASD）是启动灭火的要素；待定项（ASD是否拿出联动？案例：如果是自动模式，2022年的UPS事件会导致自喷，是否需要调整？）
 核心需求：改为自动模式（从运维和人生安全的角度），并加一道保护措施（和US一致），比如温控（联动条件）来做为一道保护措施；
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷机故障点：垫片有裂缝，需要追RCA（单独一项）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Update: 2026/5/14
-垫片有裂缝，需要追RCA（单独一项）</t>
+Update: 2026/5/21 - 
+1. 确定了方向为自动模式，下一步联合设计院，现场团队制定总体方案，经过内部评审后并与US team沟通；
+2. RCA findings sharing in next week. (TBD)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -239,47 +266,50 @@
 Team alignment:  GYA买的新的的冷机做GYA三期的恢复，GYA修好的那台发到ULA做替换，ULA有故障的那台发回工厂维修，维修好后，做两个Site的备件；
 Update: 2026/5/14 - 
 ULA坏的一台，计划发到无锡工厂，需要设备的RCA；（两台已经坏，需要原厂建议，维修内容，必要的时候工厂Visit）；
-重点关注：为什么会坏，需要采取什么措施，</t>
+重点关注：为什么会坏，需要采取什么措施，
+Update: 2026/5/21 - 
+等冷机拆卸和观察报告（JCI），再来做决定。
+故障压缩机已经寄送到无锡工厂。更换压缩机正进行制冷剂充注，预计明天上线； （维修好的冷机，放在上海办公室仓库，做为GYA/ULA的备件）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GYA冷机修复同步；</t>
+    <t>升级到AIPO政府相关部门（园区财产安全的考虑）；
+升级到电业局相关部门（对施工方式和合规等的考虑）；
+根据需要做进一步升级；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>氮气发生装置的讨论；</t>
+    <t>Update: 2026/5/14
+垫片有裂缝，需要追RCA（单独一项）；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>电池回收关注（EHS，Compliance)</t>
+    <t>持续保持同步；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Udpate 4/9 
+四个部分（压缩机，干燥机，过滤阀组，氮气发生器）集成一个Package还是分开Bid？Make Decision; 可选方案：只换氮气发生器，其他部分保持原有的品牌；（TBD）在LDI沟通中先提出想法要要求；（Proposals from LDI.)
+Update 4/25
+厂家沟通（一共4四家）：Mesa/Reno DC使用的厂家（AODC在使用），德国一家已经沟通，另外两家这周沟通，并确定下一步Engineering Team行动计划；
+Update 4/30 
+3 qualified vendors have been identified from 4. (排除了一家没有自控系统的，下周五之前汇总技术要求给到qualified venders for comments. )
+Update: 2026/5/14 - 月底有LDI的IFC图纸（计划），team review.
+Update: 2026/5/21 - Local resource pref...(FROM engineering aspect)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Udpate: 4/23
-需要AIPO公司名义注册在国家平台注册，C&amp;D探索本地供应商的可能性；变电站battery: 已经本地公司有危废协议；（&lt;100Tons, 2027元旦截止）
-Update: 2026/5/14 - 通过BM26 Battery Refresh项目来做；（Apple Prefer)</t>
+5月份US team visit来决定；（方案已经发出）现场准备EOP; (Ready Before US visit)准备临时方案/永久方案；
+Update: 2026/5/14 - 
+Prepare EOP;
+Solution: 是否可以从Small Enhancement, 从Ops Team来推进？（TBD） 
+Impact: 冷冻水补水/泄漏时候需要补充；消防需要两路供水；
+Update: 2026/5/21 - 首先看可行方案，最后提改造需求；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ULA domestic water 环网修复计划？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>岩棉问题（ULA+GYA）的讨论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Udpate: 4/23
-DH修复时可能产生的灰尘，重点关注施工方案；施工方案保证确保服务器的正常运行和无尘环境;
-Update: 2026/5/14 - 可选方案：用Patch方式，有问题的地方用铝箔胶带修复；（需要和DCO讨论），另外追溯一下破损原因（避免以后出现）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GYA烟雾报警/应急疏散讨论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ULA冷机维修</t>
+    <t>ULA红线外电线杆关注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +697,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -676,7 +707,7 @@
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" customWidth="1"/>
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="85" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="20.83203125" customWidth="1"/>
   </cols>
@@ -739,7 +770,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="32">
+    <row r="3" spans="1:9" ht="48" hidden="1">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -752,7 +783,7 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
@@ -768,7 +799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="112">
+    <row r="4" spans="1:9" ht="160">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -782,27 +813,27 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9" ht="16" hidden="1">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
@@ -810,14 +841,14 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>18</v>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -826,12 +857,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16">
+    <row r="6" spans="1:9" ht="32" hidden="1">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -839,14 +870,14 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F6" t="s">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -855,12 +886,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="192">
+    <row r="7" spans="1:9" ht="335">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
@@ -869,27 +900,27 @@
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="80">
+    <row r="8" spans="1:9" ht="96" hidden="1">
       <c r="A8" t="s">
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
@@ -898,27 +929,27 @@
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="176">
+    <row r="9" spans="1:9" ht="288">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
@@ -927,216 +958,219 @@
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="80">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="96">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="192">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="242" customHeight="1">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="114" hidden="1" customHeight="1">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="408" customHeight="1">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="224">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="64">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="64">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="112">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="C16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
         <v>50</v>
       </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="80">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="64">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="335">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="112">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="F16" t="s">
         <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
@@ -1147,33 +1181,112 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="1:9" ht="48">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="16">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="G23" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:I19" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Ongoing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I3 A5:I6 A4:D4 H4:I4 A10:I10 A7:F7 H7:I7 A8:F8 I8 A9:D9 H9:I9 A13:D13 A12:D12 H12:I12 A15:D15 A14:G14 I14 A17:D17 A16:D16 H16:I16 H15:I15 H17:I17 F4 F9 A11:D11 F11 H11:I11 F12 H13:I13 F15 F16" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I3 A5:I6 A4:F4 H4:I4 A8:I8 A7:F7 H7:I7 A14:I14 A13:F13 H13:I13 A17:F17 A15:F15 H15:I15 A19:F19 A18:D18 H18:I18 A16:F16 H16:I16 H17:I17 H19:I19 A10:I11 A9:F9 H9:I9 A12:F12 H12:I12 F18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>